--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5274,7 +5274,7 @@
         <v>46269</v>
       </c>
       <c r="B611">
-        <v>0.80913</v>
+        <v>0.8100149999999999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B611"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5277,6 +5277,14 @@
         <v>0.8100149999999999</v>
       </c>
     </row>
+    <row r="612" spans="1:2">
+      <c r="A612" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B612">
+        <v>0.8115250000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5282,7 +5282,7 @@
         <v>46276</v>
       </c>
       <c r="B612">
-        <v>0.8115250000000001</v>
+        <v>0.80757</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5282,7 +5282,7 @@
         <v>46276</v>
       </c>
       <c r="B612">
-        <v>0.80757</v>
+        <v>0.81182</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5282,7 +5282,7 @@
         <v>46276</v>
       </c>
       <c r="B612">
-        <v>0.81182</v>
+        <v>0.81514</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5282,7 +5282,7 @@
         <v>46276</v>
       </c>
       <c r="B612">
-        <v>0.81514</v>
+        <v>0.816445</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B613"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5285,6 +5285,14 @@
         <v>0.816445</v>
       </c>
     </row>
+    <row r="613" spans="1:2">
+      <c r="A613" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B613">
+        <v>0.818375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5290,7 +5290,7 @@
         <v>46283</v>
       </c>
       <c r="B613">
-        <v>0.818375</v>
+        <v>0.818925</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5290,7 +5290,7 @@
         <v>46283</v>
       </c>
       <c r="B613">
-        <v>0.818925</v>
+        <v>0.8248800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5290,7 +5290,7 @@
         <v>46283</v>
       </c>
       <c r="B613">
-        <v>0.8248800000000001</v>
+        <v>0.8256600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5290,7 +5290,7 @@
         <v>46283</v>
       </c>
       <c r="B613">
-        <v>0.8256600000000001</v>
+        <v>0.82211</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B613"/>
+  <dimension ref="A1:B614"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5293,6 +5293,14 @@
         <v>0.82211</v>
       </c>
     </row>
+    <row r="614" spans="1:2">
+      <c r="A614" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B614">
+        <v>0.8189949999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5298,7 +5298,7 @@
         <v>46290</v>
       </c>
       <c r="B614">
-        <v>0.8189949999999999</v>
+        <v>0.82284</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5298,7 +5298,7 @@
         <v>46290</v>
       </c>
       <c r="B614">
-        <v>0.82284</v>
+        <v>0.827825</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5298,7 +5298,7 @@
         <v>46290</v>
       </c>
       <c r="B614">
-        <v>0.827825</v>
+        <v>0.8285</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5298,7 +5298,7 @@
         <v>46290</v>
       </c>
       <c r="B614">
-        <v>0.8285</v>
+        <v>0.8286450000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B614"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5301,6 +5301,14 @@
         <v>0.8286450000000001</v>
       </c>
     </row>
+    <row r="615" spans="1:2">
+      <c r="A615" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B615">
+        <v>0.8329800000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5306,7 +5306,7 @@
         <v>46297</v>
       </c>
       <c r="B615">
-        <v>0.8329800000000001</v>
+        <v>0.83474</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5306,7 +5306,7 @@
         <v>46297</v>
       </c>
       <c r="B615">
-        <v>0.83474</v>
+        <v>0.8349</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5306,7 +5306,7 @@
         <v>46297</v>
       </c>
       <c r="B615">
-        <v>0.8349</v>
+        <v>0.826435</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5306,7 +5306,7 @@
         <v>46297</v>
       </c>
       <c r="B615">
-        <v>0.826435</v>
+        <v>0.8287599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B615"/>
+  <dimension ref="A1:B616"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5309,6 +5309,14 @@
         <v>0.8287599999999999</v>
       </c>
     </row>
+    <row r="616" spans="1:2">
+      <c r="A616" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B616">
+        <v>0.832335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5314,7 +5314,7 @@
         <v>46304</v>
       </c>
       <c r="B616">
-        <v>0.832335</v>
+        <v>0.8338650000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5314,7 +5314,7 @@
         <v>46304</v>
       </c>
       <c r="B616">
-        <v>0.8338650000000001</v>
+        <v>0.8311200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5314,7 +5314,7 @@
         <v>46304</v>
       </c>
       <c r="B616">
-        <v>0.8311200000000001</v>
+        <v>0.829295</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B616"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5317,6 +5317,14 @@
         <v>0.829295</v>
       </c>
     </row>
+    <row r="617" spans="1:2">
+      <c r="A617" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B617">
+        <v>0.8321000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5322,7 +5322,7 @@
         <v>46311</v>
       </c>
       <c r="B617">
-        <v>0.8321000000000001</v>
+        <v>0.8331649999999999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B616"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5317,14 +5317,6 @@
         <v>0.829295</v>
       </c>
     </row>
-    <row r="617" spans="1:2">
-      <c r="A617" s="3">
-        <v>46311</v>
-      </c>
-      <c r="B617">
-        <v>0.8331649999999999</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B616"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5317,6 +5317,14 @@
         <v>0.829295</v>
       </c>
     </row>
+    <row r="617" spans="1:2">
+      <c r="A617" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B617">
+        <v>0.83012</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCHF_diff_0th_diff.xlsx
+++ b/public/data/files/USDCHF_diff_0th_diff.xlsx
@@ -5322,7 +5322,7 @@
         <v>46311</v>
       </c>
       <c r="B617">
-        <v>0.83012</v>
+        <v>0.82343</v>
       </c>
     </row>
   </sheetData>
